--- a/data/trans_bre/IP17-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 18,13</t>
+          <t>-2,34; 18,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 10,12</t>
+          <t>-8,75; 11,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 7,94</t>
+          <t>-10,27; 8,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 10,23</t>
+          <t>-14,25; 10,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 63,57</t>
+          <t>-6,4; 64,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 30,13</t>
+          <t>-19,25; 31,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 26,39</t>
+          <t>-26,48; 29,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 41,73</t>
+          <t>-39,53; 43,77</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 1,46</t>
+          <t>-10,99; 1,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 5,51</t>
+          <t>-7,85; 4,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 7,57</t>
+          <t>-4,34; 7,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 5,51</t>
+          <t>-7,9; 5,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 7,12</t>
+          <t>-39,88; 5,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 23,72</t>
+          <t>-28,21; 20,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 46,08</t>
+          <t>-20,7; 44,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 37,33</t>
+          <t>-36,62; 38,26</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 3,06</t>
+          <t>-10,84; 3,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 11,48</t>
+          <t>-1,43; 11,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 5,05</t>
+          <t>-8,16; 4,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 7,67</t>
+          <t>-7,0; 8,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 19,49</t>
+          <t>-49,72; 24,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 123,51</t>
+          <t>-9,63; 128,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 32,97</t>
+          <t>-36,89; 32,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 54,02</t>
+          <t>-34,0; 57,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 0,07</t>
+          <t>-11,11; -0,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 3,66</t>
+          <t>-7,66; 3,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 8,33</t>
+          <t>-2,82; 8,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -0,12</t>
+          <t>-10,3; 0,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 1,47</t>
+          <t>-58,46; -2,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 32,48</t>
+          <t>-45,78; 31,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 102,0</t>
+          <t>-23,84; 101,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,63; -0,59</t>
+          <t>-59,74; 2,71</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,3</t>
+          <t>-6,5; 0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,81</t>
+          <t>-3,56; 3,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,43</t>
+          <t>-2,71; 4,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,19</t>
+          <t>-6,11; 1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 1,41</t>
+          <t>-26,78; 2,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 18,17</t>
+          <t>-14,3; 18,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 25,54</t>
+          <t>-12,32; 22,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 8,15</t>
+          <t>-31,29; 10,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 18,16</t>
+          <t>-2,77; 17,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 11,15</t>
+          <t>-8,22; 10,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 8,98</t>
+          <t>-10,32; 8,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 10,99</t>
+          <t>-13,84; 11,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 64,04</t>
+          <t>-9,25; 61,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 31,27</t>
+          <t>-17,94; 31,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 29,08</t>
+          <t>-26,55; 28,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 43,77</t>
+          <t>-39,21; 46,31</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 1,13</t>
+          <t>-9,97; 1,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 4,57</t>
+          <t>-7,81; 4,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 7,26</t>
+          <t>-4,65; 6,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 5,7</t>
+          <t>-7,8; 6,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,88; 5,55</t>
+          <t>-37,0; 8,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 20,41</t>
+          <t>-28,01; 21,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 44,4</t>
+          <t>-22,95; 41,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 38,26</t>
+          <t>-35,5; 42,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 3,62</t>
+          <t>-11,29; 3,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 11,76</t>
+          <t>-2,23; 11,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 4,9</t>
+          <t>-8,01; 5,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 8,21</t>
+          <t>-6,19; 9,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,72; 24,45</t>
+          <t>-48,64; 21,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 128,62</t>
+          <t>-15,02; 112,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 32,73</t>
+          <t>-36,19; 36,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 57,79</t>
+          <t>-30,97; 67,07</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -0,43</t>
+          <t>-11,63; -0,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 3,57</t>
+          <t>-7,8; 4,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 8,69</t>
+          <t>-2,94; 8,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 0,2</t>
+          <t>-10,52; 0,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,46; -2,62</t>
+          <t>-59,96; -3,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 31,32</t>
+          <t>-46,03; 36,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 101,05</t>
+          <t>-22,8; 99,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,74; 2,71</t>
+          <t>-61,38; 0,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,45</t>
+          <t>-6,11; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,89</t>
+          <t>-3,24; 4,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,1</t>
+          <t>-2,62; 4,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,53</t>
+          <t>-5,76; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 2,8</t>
+          <t>-25,52; 4,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 18,47</t>
+          <t>-13,53; 22,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 22,8</t>
+          <t>-12,8; 22,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 10,46</t>
+          <t>-30,44; 7,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,62%</t>
+          <t>-4,78%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 17,9</t>
+          <t>-3,21; 18,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 10,89</t>
+          <t>-7,88; 10,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 8,25</t>
+          <t>-11,41; 7,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 11,11</t>
+          <t>-13,51; 10,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 61,53</t>
+          <t>-8,28; 63,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 31,64</t>
+          <t>-17,66; 30,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 28,04</t>
+          <t>-28,75; 26,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 46,31</t>
+          <t>-37,57; 43,74</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,19%</t>
+          <t>-5,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 1,49</t>
+          <t>-10,58; 1,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 4,8</t>
+          <t>-7,76; 5,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 6,74</t>
+          <t>-4,44; 7,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 6,59</t>
+          <t>-8,33; 5,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 8,27</t>
+          <t>-38,92; 7,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 21,78</t>
+          <t>-28,16; 23,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 41,68</t>
+          <t>-20,12; 46,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 42,97</t>
+          <t>-38,15; 36,43</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>-4,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 3,64</t>
+          <t>-11,14; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 11,18</t>
+          <t>-1,85; 11,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 5,22</t>
+          <t>-8,78; 5,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 9,24</t>
+          <t>-8,0; 5,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 21,11</t>
+          <t>-49,12; 19,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 112,92</t>
+          <t>-12,13; 123,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 36,13</t>
+          <t>-36,97; 32,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 67,07</t>
+          <t>-36,17; 42,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,02</t>
+          <t>-4,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,07%</t>
+          <t>-30,21%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,63; -0,81</t>
+          <t>-10,51; 0,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 4,29</t>
+          <t>-8,47; 3,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 8,14</t>
+          <t>-2,49; 8,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 0,08</t>
+          <t>-9,33; 0,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,96; -3,84</t>
+          <t>-56,35; 1,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 36,73</t>
+          <t>-49,17; 32,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 99,28</t>
+          <t>-20,19; 102,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 0,31</t>
+          <t>-54,97; 7,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-12,7%</t>
+          <t>-12,55%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,94</t>
+          <t>-6,45; 0,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,44</t>
+          <t>-3,79; 3,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,06</t>
+          <t>-2,61; 4,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,16</t>
+          <t>-6,0; 0,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 4,47</t>
+          <t>-26,75; 1,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 22,1</t>
+          <t>-15,18; 18,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 22,07</t>
+          <t>-12,18; 25,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 7,61</t>
+          <t>-30,64; 6,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-2,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-4,78%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>8.132151339507853</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.255567071249403</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.8079478952432995</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.451793517181432</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2459045388562573</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.03154233246850377</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.02337764416951279</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.04779147881099878</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,21; 18,13</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,88; 10,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-11,41; 7,94</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 10,9</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-8,28; 63,57</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-17,66; 30,13</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-28,75; 26,39</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-37,57; 43,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.211336418346844</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.876879069812455</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-11.40930707192202</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-13.51480812441997</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.08281998534967379</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.176572118941967</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2875385876824109</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3757153575433731</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>18.12798959632033</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.11785526136041</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.939722798824995</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.90430352603401</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.6357348025949451</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3012807960823795</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2638533944566667</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.4373758112357504</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-18,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-6,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-5,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-10,58; 1,46</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,76; 5,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 7,57</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-8,33; 5,53</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-38,92; 7,12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-28,16; 23,72</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-20,12; 46,08</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-38,15; 36,43</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-4.394812373957047</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.713021494907341</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.50849042530127</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.048250252015498</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1826356662805629</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.06839127006393429</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.07935209936854962</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.0566526752688724</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,92</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,68</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-20,2%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-9,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-4,79%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-10.58363248081146</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.758805888112001</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.43892768596952</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-8.331622512749142</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3892108201451369</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2816282814003589</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2012022251127869</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3815018519616334</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-11,14; 3,06</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,85; 11,48</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,78; 5,05</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,0; 5,9</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-49,12; 19,49</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-12,13; 123,51</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-36,97; 32,97</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-36,17; 42,73</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.463555890294644</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.510981168632396</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.572364764590085</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.526931337213309</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.07124776137109132</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2371794869299807</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4608367336661494</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.364289722818785</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,65</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,81</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-4,3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-35,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-13,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-30,21%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.916650115916506</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.677031066409562</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.775595689217371</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.8507765769672576</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.201974415755263</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3721102336123055</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.09267277607168725</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.04787573584549726</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-10,51; 0,07</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,47; 3,66</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; 8,33</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-9,33; 0,64</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-56,35; 1,47</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-49,17; 32,48</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-20,19; 102,0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-54,97; 7,16</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-11.1391643625667</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.845960924172806</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.782106288671656</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.999560857388325</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4912104278527019</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1213164019929762</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3697012379295935</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3616942827369886</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.060056216123827</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.48046163168716</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.047910795760762</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.898041835170599</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1949041480810132</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.235083940479034</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3297084929523965</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4273010428707348</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-5.648502435923068</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.962056257094123</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.812131574723012</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-4.299907350486697</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3506549270908192</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1381816497109858</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2600270882210576</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3020520436813121</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-10.50740954992668</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.467072327702356</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.489866629231735</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-9.334100597538301</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5634982065437419</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4917173900395866</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.201924357623001</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.549684527028388</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.06569497756781406</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.655608296249664</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.331490481326018</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.6438627947772126</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.01471917559469216</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3247662925712136</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.019981245309766</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.07161656421937605</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-12,4%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-12,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-6,45; 0,3</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 3,81</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 4,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; 0,93</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-26,75; 1,41</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-15,18; 18,17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-12,18; 25,54</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-30,64; 6,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.777549745515398</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.2721518253771343</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.742484680828992</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.179492267035144</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1240348381646639</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.01198507573561369</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03764575658544685</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1254872386479975</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-6.445311372306225</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.787330492014624</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.61348695625298</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.000409658346887</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.267513060741268</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1518363107115851</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1217768689652747</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3064241057909387</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.3033190192871209</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.813732180073707</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.431683644868994</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.9327636783477417</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.01408979416886108</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1816768411742733</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2553692873691689</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.05996079901019331</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
